--- a/data/trans_dic/P22$concerEmp-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,42 +717,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,33</t>
+          <t>1,16; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,38</t>
+          <t>0,55; 2,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,08</t>
+          <t>0,22; 2,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,74</t>
+          <t>0,0; 0,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,42</t>
+          <t>0,14; 1,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,06</t>
+          <t>0,18; 1,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -762,17 +762,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,56</t>
+          <t>0,48; 1,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,87</t>
+          <t>0,13; 0,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,41</t>
+          <t>0,31; 1,31</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,87</t>
+          <t>1,7; 3,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,37</t>
+          <t>0,7; 2,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,55</t>
+          <t>0,26; 1,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,18</t>
+          <t>0,44; 2,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,12</t>
+          <t>0,12; 1,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,56</t>
+          <t>0,0; 0,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,08</t>
+          <t>0,19; 1,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,68</t>
+          <t>0,07; 0,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,19</t>
+          <t>1,03; 2,25</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,25</t>
+          <t>0,37; 1,27</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,08</t>
+          <t>0,29; 1,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,27</t>
+          <t>0,38; 1,27</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,07</t>
+          <t>1,58; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,06</t>
+          <t>0,8; 2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,49</t>
+          <t>0,61; 2,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,87</t>
+          <t>0,4; 1,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,67</t>
+          <t>0,05; 0,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,55</t>
+          <t>1,22; 2,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,65</t>
+          <t>0,52; 1,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,18</t>
+          <t>0,33; 1,16</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,66</t>
+          <t>1,04; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,15</t>
+          <t>0,2; 1,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,6</t>
+          <t>0,3; 1,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,76</t>
+          <t>1,42; 3,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,36</t>
+          <t>0,29; 1,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,14</t>
+          <t>0,2; 1,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,14</t>
+          <t>0,19; 1,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,24</t>
+          <t>0,82; 2,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,64</t>
+          <t>0,76; 1,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,94</t>
+          <t>0,29; 0,92</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,1</t>
+          <t>0,35; 1,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,5</t>
+          <t>1,27; 2,59</t>
         </is>
       </c>
     </row>
@@ -1277,52 +1277,52 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,8</t>
+          <t>1,77; 2,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,57</t>
+          <t>0,84; 1,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,92</t>
+          <t>0,31; 0,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 1,93</t>
+          <t>0,93; 1,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 0,86</t>
+          <t>0,34; 0,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,62</t>
+          <t>0,22; 0,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,59</t>
+          <t>0,2; 0,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,91</t>
+          <t>0,43; 0,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 1,68</t>
+          <t>1,11; 1,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,02</t>
+          <t>0,56; 0,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,29</t>
+          <t>0,78; 1,3</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguro Médico concertado por su empresa</t>
+          <t>Población que, al menos, es beneficiaria de seguro médico concertado por su empresa (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8019; 23018</t>
+          <t>7992; 24406</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3704; 16725</t>
+          <t>3900; 16425</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 11121</t>
+          <t>0; 9953</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2154; 13224</t>
+          <t>1429; 14340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5084</t>
+          <t>0; 4498</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1001; 9918</t>
+          <t>996; 9008</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6213</t>
+          <t>0; 6251</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1180; 7167</t>
+          <t>1203; 6937</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8116; 24687</t>
+          <t>8085; 24657</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6966; 21909</t>
+          <t>6661; 20875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>952; 11740</t>
+          <t>1753; 11059</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4205; 18478</t>
+          <t>4123; 17141</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15774; 37227</t>
+          <t>16345; 36944</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7475; 24114</t>
+          <t>7097; 23907</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2421; 15833</t>
+          <t>2629; 16484</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5034; 26062</t>
+          <t>5290; 25080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1152; 10844</t>
+          <t>1147; 10154</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5824</t>
+          <t>0; 3928</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1907; 11240</t>
+          <t>1933; 11171</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>659; 6513</t>
+          <t>663; 6387</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>20092; 42234</t>
+          <t>19950; 43415</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8250; 25598</t>
+          <t>7526; 25947</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6191; 22181</t>
+          <t>5972; 21719</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7739; 27253</t>
+          <t>8087; 27388</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11018; 27554</t>
+          <t>10707; 26888</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6625; 23180</t>
+          <t>6071; 21331</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 9530</t>
+          <t>0; 8555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4123; 17558</t>
+          <t>4265; 16644</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2650; 12754</t>
+          <t>2768; 12807</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7640</t>
+          <t>0; 7530</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2043</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>466; 6216</t>
+          <t>504; 6419</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15611; 34654</t>
+          <t>16593; 35775</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8146; 25362</t>
+          <t>7998; 24351</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 9592</t>
+          <t>0; 9619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4781; 19349</t>
+          <t>5332; 19057</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9687; 25006</t>
+          <t>9752; 25032</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1940; 10932</t>
+          <t>1916; 10690</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2917; 14980</t>
+          <t>2793; 14573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13382; 34883</t>
+          <t>13198; 34166</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3091; 14077</t>
+          <t>2986; 13572</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2022; 12017</t>
+          <t>2053; 13470</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1929; 11889</t>
+          <t>2032; 11725</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9103; 24494</t>
+          <t>8961; 23958</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14928; 32427</t>
+          <t>14988; 32588</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5775; 18827</t>
+          <t>5818; 18368</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6811; 21833</t>
+          <t>6927; 21821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26427; 50582</t>
+          <t>25736; 52206</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>58910; 91539</t>
+          <t>57796; 91154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>27146; 53641</t>
+          <t>28703; 54769</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11358; 31139</t>
+          <t>10391; 31425</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33658; 66724</t>
+          <t>32078; 65780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11173; 28937</t>
+          <t>11325; 29491</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7093; 22154</t>
+          <t>7912; 22079</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6866; 21055</t>
+          <t>7040; 21098</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15751; 33438</t>
+          <t>15663; 33003</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>74200; 112004</t>
+          <t>73991; 113186</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38600; 70893</t>
+          <t>38861; 69011</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22121; 45723</t>
+          <t>21825; 45532</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>56288; 91591</t>
+          <t>55461; 92328</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$concerEmp-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P22$concerEmp-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,53</t>
+          <t>1,15; 3,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,33</t>
+          <t>0,55; 2,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,26</t>
+          <t>0,3; 2,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,65</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,29</t>
+          <t>0,14; 1,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,03</t>
+          <t>0,18; 1,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,79</t>
+          <t>0,59; 1,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,49</t>
+          <t>0,47; 1,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,82</t>
+          <t>0,13; 0,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,31</t>
+          <t>0,34; 1,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,85</t>
+          <t>1,64; 3,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,35</t>
+          <t>0,72; 2,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,61</t>
+          <t>0,23; 1,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,1</t>
+          <t>0,66; 2,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,05</t>
+          <t>0,12; 1,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,07</t>
+          <t>0,19; 1,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,67</t>
+          <t>0,06; 0,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,25</t>
+          <t>1,07; 2,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,27</t>
+          <t>0,39; 1,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,05</t>
+          <t>0,3; 1,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,27</t>
+          <t>0,41; 1,3</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,97</t>
+          <t>1,57; 3,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,82</t>
+          <t>0,82; 3,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,36</t>
+          <t>0,44; 2,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,87</t>
+          <t>0,38; 1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,69</t>
+          <t>0,08; 0,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,63</t>
+          <t>1,23; 2,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,52; 1,59</t>
+          <t>0,51; 1,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,16</t>
+          <t>0,34; 1,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1137,32 +1137,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,66</t>
+          <t>1,03; 2,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,13</t>
+          <t>0,21; 1,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,56</t>
+          <t>0,31; 1,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,69</t>
+          <t>1,5; 3,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,31</t>
+          <t>0,21; 1,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,28</t>
+          <t>0,2; 1,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,19</t>
+          <t>0,92; 2,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,65</t>
+          <t>0,77; 1,72</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,92</t>
+          <t>0,26; 0,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,1</t>
+          <t>0,35; 1,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,59</t>
+          <t>1,35; 2,52</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,79</t>
+          <t>1,76; 2,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,6</t>
+          <t>0,8; 1,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 0,93</t>
+          <t>0,32; 0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,9</t>
+          <t>1,08; 2,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 0,87</t>
+          <t>0,32; 0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,62</t>
+          <t>0,19; 0,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,6</t>
+          <t>0,19; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,9</t>
+          <t>0,47; 0,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,7</t>
+          <t>1,1; 1,7</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,99</t>
+          <t>0,55; 0,99</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,66</t>
+          <t>0,32; 0,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,3</t>
+          <t>0,81; 1,32</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>9688</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7992; 24406</t>
+          <t>7973; 23533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3900; 16425</t>
+          <t>3853; 17103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9953</t>
+          <t>0; 10925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1429; 14340</t>
+          <t>2084; 14434</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4498</t>
+          <t>0; 5373</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>996; 9008</t>
+          <t>995; 10100</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6251</t>
+          <t>0; 5303</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1203; 6937</t>
+          <t>1339; 7791</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8085; 24657</t>
+          <t>8104; 24244</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6661; 20875</t>
+          <t>6528; 20741</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1753; 11059</t>
+          <t>1754; 11683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4123; 17141</t>
+          <t>4791; 18372</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>13911</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15629</t>
+          <t>16807</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16345; 36944</t>
+          <t>15753; 36320</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7097; 23907</t>
+          <t>7339; 23496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2629; 16484</t>
+          <t>2361; 15405</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5290; 25080</t>
+          <t>6959; 25424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1147; 10154</t>
+          <t>1147; 9896</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3928</t>
+          <t>0; 4878</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1933; 11171</t>
+          <t>1942; 12150</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>663; 6387</t>
+          <t>669; 6884</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19950; 43415</t>
+          <t>20604; 42557</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7526; 25947</t>
+          <t>8040; 25271</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5972; 21719</t>
+          <t>6262; 22403</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8087; 27388</t>
+          <t>8699; 27528</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2098</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10790</t>
+          <t>11161</t>
         </is>
       </c>
     </row>
@@ -2061,32 +2061,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10707; 26888</t>
+          <t>10631; 26883</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6071; 21331</t>
+          <t>6215; 23180</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 8555</t>
+          <t>0; 9660</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4265; 16644</t>
+          <t>3506; 16408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2768; 12807</t>
+          <t>2621; 12880</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 7530</t>
+          <t>0; 7617</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2096,27 +2096,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>504; 6419</t>
+          <t>667; 5747</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>16593; 35775</t>
+          <t>16758; 36823</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7998; 24351</t>
+          <t>7904; 24332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 9619</t>
+          <t>0; 9545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5332; 19057</t>
+          <t>5554; 20048</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21668</t>
+          <t>23467</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>16299</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36972</t>
+          <t>39766</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9752; 25032</t>
+          <t>9652; 25142</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1916; 10690</t>
+          <t>1957; 10550</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2793; 14573</t>
+          <t>2865; 15265</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13198; 34166</t>
+          <t>14803; 37284</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2986; 13572</t>
+          <t>2147; 12367</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2053; 13470</t>
+          <t>2083; 12071</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2032; 11725</t>
+          <t>2028; 11652</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8961; 23958</t>
+          <t>10315; 24899</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14988; 32588</t>
+          <t>15291; 33938</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5818; 18368</t>
+          <t>5122; 18670</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6927; 21821</t>
+          <t>6948; 22027</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25736; 52206</t>
+          <t>28416; 53125</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48766</t>
+          <t>52667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23200</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71966</t>
+          <t>77422</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57796; 91154</t>
+          <t>57515; 93141</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>28703; 54769</t>
+          <t>27511; 55618</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10391; 31425</t>
+          <t>10884; 32188</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32078; 65780</t>
+          <t>38292; 72093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>11325; 29491</t>
+          <t>10797; 28701</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7912; 22079</t>
+          <t>6884; 21084</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7040; 21098</t>
+          <t>6799; 20757</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>15663; 33003</t>
+          <t>17557; 35815</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>73991; 113186</t>
+          <t>73090; 113063</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38861; 69011</t>
+          <t>38721; 69164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21825; 45532</t>
+          <t>22216; 48325</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55461; 92328</t>
+          <t>58899; 95990</t>
         </is>
       </c>
     </row>
